--- a/Analysis/Hybrid_Ablation/hybrid_order_reversal.xlsx
+++ b/Analysis/Hybrid_Ablation/hybrid_order_reversal.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP5"/>
+  <dimension ref="A1:AR5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,11 +628,21 @@
           <t>between_net_correct_gain</t>
         </is>
       </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>perm_choice_p_holm</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>perm_param_p_holm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -641,16 +651,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.001161306365271231</v>
+        <v>-0.003851933044625611</v>
       </c>
       <c r="D2" t="n">
-        <v>0.679098679098679</v>
+        <v>0.8383838383838383</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05433782730154824</v>
+        <v>0.004095884045194398</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000777000777000777</v>
+        <v>0.3022533022533023</v>
       </c>
       <c r="G2" t="n">
         <v>1287</v>
@@ -659,52 +669,52 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.951697946955679</v>
+        <v>0.9336717811392492</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5834082297999822</v>
+        <v>0.3684153671368089</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0001640554484952927</v>
+        <v>-0.004793475533937497</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05642499373389809</v>
+        <v>0.008804294662229706</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007936507936507936</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="O2" t="n">
         <v>252</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003103221564760061</v>
+        <v>-0.0061846018160997</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03363576594345818</v>
+        <v>0.007296962646301697</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.25</v>
       </c>
       <c r="T2" t="n">
         <v>56</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.001161306365271231</v>
+        <v>-0.003851933044625611</v>
       </c>
       <c r="V2" t="n">
-        <v>0.679098679098679</v>
+        <v>0.8383838383838383</v>
       </c>
       <c r="W2" t="n">
-        <v>0.05433782730154824</v>
+        <v>0.004095884045194398</v>
       </c>
       <c r="X2" t="n">
-        <v>0.000777000777000777</v>
+        <v>0.3022533022533023</v>
       </c>
       <c r="Y2" t="n">
         <v>1287</v>
@@ -716,37 +726,37 @@
         <v>5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.952613998539964</v>
+        <v>0.9253426472485472</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9329896907216495</v>
+        <v>0.9050632911392406</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.9512820512820512</v>
+        <v>0.9304930211750196</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.9384615384615385</v>
+        <v>0.9125</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.9521120803595029</v>
+        <v>0.9327113097457209</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9025974025974026</v>
       </c>
       <c r="AH2" t="b">
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.5787870744358111</v>
+        <v>0.3799816088939457</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.5651282051282051</v>
+        <v>0.3782410270787036</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5155326460481099</v>
+        <v>0.3703070233240949</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.2265625</v>
+        <v>0.0703125</v>
       </c>
       <c r="AM2" t="n">
         <v>1</v>
@@ -758,13 +768,19 @@
         <v>25</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.48</v>
+        <v>-0.92</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -773,16 +789,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.003851933044625611</v>
+        <v>-0.001161306365271231</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8383838383838383</v>
+        <v>0.679098679098679</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004095884045194398</v>
+        <v>0.05433782730154824</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3022533022533023</v>
+        <v>0.000777000777000777</v>
       </c>
       <c r="G3" t="n">
         <v>1287</v>
@@ -791,52 +807,52 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9336717811392492</v>
+        <v>0.951697946955679</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3684153671368089</v>
+        <v>0.5834082297999822</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.004793475533937497</v>
+        <v>-0.0001640554484952927</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008804294662229706</v>
+        <v>0.05642499373389809</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.007936507936507936</v>
       </c>
       <c r="O3" t="n">
         <v>252</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0061846018160997</v>
+        <v>-0.003103221564760061</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.875</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007296962646301697</v>
+        <v>0.03363576594345818</v>
       </c>
       <c r="S3" t="n">
-        <v>0.25</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="T3" t="n">
         <v>56</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.003851933044625611</v>
+        <v>-0.001161306365271231</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8383838383838383</v>
+        <v>0.679098679098679</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004095884045194398</v>
+        <v>0.05433782730154824</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3022533022533023</v>
+        <v>0.000777000777000777</v>
       </c>
       <c r="Y3" t="n">
         <v>1287</v>
@@ -848,37 +864,37 @@
         <v>5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9253426472485472</v>
+        <v>0.952613998539964</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.9050632911392406</v>
+        <v>0.9329896907216495</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.9304930211750196</v>
+        <v>0.9512820512820512</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.9125</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.9327113097457209</v>
+        <v>0.9521120803595029</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.9025974025974026</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="AH3" t="b">
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.3799816088939457</v>
+        <v>0.5787870744358111</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.3782410270787036</v>
+        <v>0.5651282051282051</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.3703070233240949</v>
+        <v>0.5155326460481099</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0703125</v>
+        <v>0.2265625</v>
       </c>
       <c r="AM3" t="n">
         <v>1</v>
@@ -890,7 +906,13 @@
         <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.92</v>
+        <v>1.48</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.006216006216006216</v>
       </c>
     </row>
     <row r="4">
@@ -1024,6 +1046,12 @@
       <c r="AP4" t="n">
         <v>0.4</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1155,6 +1183,12 @@
       </c>
       <c r="AP5" t="n">
         <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.006216006216006216</v>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1265,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1250,31 +1284,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>194</v>
+        <v>153</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9536082474226805</v>
+        <v>0.9150326797385621</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5773195876288659</v>
+        <v>0.3660130718954248</v>
       </c>
       <c r="H2" t="n">
-        <v>194</v>
+        <v>153</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2890625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1293,31 +1327,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9484536082474226</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5360824742268041</v>
+        <v>0.4161490683229814</v>
       </c>
       <c r="H3" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1796875</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1336,31 +1370,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9378238341968912</v>
+        <v>0.9050632911392406</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5751295336787565</v>
+        <v>0.3860759493670886</v>
       </c>
       <c r="H4" t="n">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3876953125</v>
+        <v>0.79052734375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1379,31 +1413,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9690721649484536</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5927835051546392</v>
+        <v>0.3397435897435898</v>
       </c>
       <c r="H5" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0.375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1422,31 +1456,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9384615384615385</v>
+        <v>0.930379746835443</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5538461538461539</v>
+        <v>0.4050632911392405</v>
       </c>
       <c r="H6" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.548828125</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1465,22 +1499,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9639175257731959</v>
+        <v>0.90625</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5927835051546392</v>
+        <v>0.4125</v>
       </c>
       <c r="H7" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -1489,7 +1523,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1508,22 +1542,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9692307692307692</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5948717948717949</v>
+        <v>0.3806451612903226</v>
       </c>
       <c r="H8" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -1532,7 +1566,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1551,31 +1585,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9329896907216495</v>
+        <v>0.9135802469135802</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5876288659793815</v>
+        <v>0.3580246913580247</v>
       </c>
       <c r="H9" t="n">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.79052734375</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1594,31 +1628,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
-        <v>0.958974358974359</v>
+        <v>0.9430379746835443</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5794871794871795</v>
+        <v>0.3481012658227848</v>
       </c>
       <c r="H10" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7265625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1637,22 +1671,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9536082474226805</v>
+        <v>0.925</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5979381443298969</v>
+        <v>0.3875</v>
       </c>
       <c r="H11" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -1661,7 +1695,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1680,22 +1714,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9290322580645162</v>
       </c>
       <c r="G12" t="n">
-        <v>0.558974358974359</v>
+        <v>0.4129032258064516</v>
       </c>
       <c r="H12" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -1704,7 +1738,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1723,31 +1757,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9435897435897436</v>
+        <v>0.9371069182389937</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.3773584905660378</v>
       </c>
       <c r="H13" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" t="n">
         <v>3</v>
       </c>
-      <c r="J13" t="n">
-        <v>5</v>
-      </c>
       <c r="K13" t="n">
-        <v>0.7265625</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1766,31 +1800,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5794871794871795</v>
+        <v>0.4150943396226415</v>
       </c>
       <c r="H14" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.5078125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1809,31 +1843,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9125</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5435897435897435</v>
+        <v>0.39375</v>
       </c>
       <c r="H15" t="n">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5078125</v>
+        <v>0.5810546875</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1852,31 +1886,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9384615384615385</v>
+        <v>0.9245283018867925</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5794871794871795</v>
+        <v>0.4213836477987422</v>
       </c>
       <c r="H16" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.3876953125</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1895,31 +1929,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9435897435897436</v>
+        <v>0.9245283018867925</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5487179487179488</v>
+        <v>0.3396226415094339</v>
       </c>
       <c r="H17" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I17" t="n">
         <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.7744140625</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,31 +1972,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="F18" t="n">
-        <v>0.958974358974359</v>
+        <v>0.9192546583850931</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.422360248447205</v>
       </c>
       <c r="H18" t="n">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="I18" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" t="n">
         <v>5</v>
       </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
       <c r="K18" t="n">
-        <v>0.7265625</v>
+        <v>0.7744140625</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1981,31 +2015,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9435897435897436</v>
+        <v>0.9245283018867925</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5743589743589743</v>
+        <v>0.3647798742138365</v>
       </c>
       <c r="H19" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.75390625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2024,31 +2058,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9794871794871794</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5487179487179488</v>
+        <v>0.3475609756097561</v>
       </c>
       <c r="H20" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.25</v>
+        <v>0.2265625</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2067,16 +2101,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9382716049382716</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5487179487179488</v>
+        <v>0.3950617283950617</v>
       </c>
       <c r="H21" t="n">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="I21" t="n">
         <v>4</v>
@@ -2091,7 +2125,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2110,31 +2144,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9503105590062112</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5743589743589743</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="H22" t="n">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0.0703125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2153,22 +2187,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9447852760736196</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5794871794871795</v>
+        <v>0.3803680981595092</v>
       </c>
       <c r="H23" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
         <v>5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -2177,7 +2211,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2196,31 +2230,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9435897435897436</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.3696969696969697</v>
       </c>
       <c r="H24" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.75390625</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2239,31 +2273,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9742268041237113</v>
+        <v>0.9503105590062112</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5515463917525774</v>
+        <v>0.3788819875776397</v>
       </c>
       <c r="H25" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
         <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0.453125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2282,31 +2316,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9435897435897436</v>
+        <v>0.8987341772151899</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.3291139240506329</v>
       </c>
       <c r="H26" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2890625</v>
+        <v>0.803619384765625</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2325,31 +2359,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9435897435897436</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5692307692307692</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1796875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2368,31 +2402,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9329896907216495</v>
+        <v>0.9074074074074074</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5618556701030928</v>
+        <v>0.3271604938271605</v>
       </c>
       <c r="H28" t="n">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3876953125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2411,31 +2445,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5846153846153846</v>
+        <v>0.335483870967742</v>
       </c>
       <c r="H29" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2454,16 +2488,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9639175257731959</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5670103092783505</v>
+        <v>0.3653846153846154</v>
       </c>
       <c r="H30" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="I30" t="n">
         <v>4</v>
@@ -2478,7 +2512,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2497,31 +2531,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9548387096774194</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5692307692307692</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="H31" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
         <v>3</v>
       </c>
-      <c r="J31" t="n">
-        <v>6</v>
-      </c>
       <c r="K31" t="n">
-        <v>0.5078125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2540,31 +2574,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9282051282051282</v>
+        <v>0.9556962025316456</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5692307692307692</v>
+        <v>0.2911392405063291</v>
       </c>
       <c r="H32" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
         <v>4</v>
       </c>
-      <c r="J32" t="n">
-        <v>8</v>
-      </c>
       <c r="K32" t="n">
-        <v>0.3876953125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2583,31 +2617,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9381443298969072</v>
+        <v>0.9125</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5721649484536082</v>
+        <v>0.38125</v>
       </c>
       <c r="H33" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
         <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>0.548828125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2626,31 +2660,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F34" t="n">
-        <v>0.958974358974359</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5794871794871795</v>
+        <v>0.4240506329113924</v>
       </c>
       <c r="H34" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,31 +2703,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9536082474226805</v>
+        <v>0.9559748427672956</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5979381443298969</v>
+        <v>0.4654088050314465</v>
       </c>
       <c r="H35" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7265625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2712,31 +2746,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9375</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.325</v>
       </c>
       <c r="H36" t="n">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K36" t="n">
-        <v>0.625</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2755,31 +2789,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9512195121951219</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5948717948717949</v>
+        <v>0.3780487804878049</v>
       </c>
       <c r="H37" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>0.548828125</v>
+        <v>0.2890625</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2798,31 +2832,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9536082474226805</v>
+        <v>0.9207317073170732</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6185567010309279</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="H38" t="n">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>0.453125</v>
+        <v>0.5810546875</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2841,31 +2875,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.9329268292682927</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6358974358974359</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="H39" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0.548828125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2884,31 +2918,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="F40" t="n">
-        <v>0.958974358974359</v>
+        <v>0.9554140127388535</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.3885350318471338</v>
       </c>
       <c r="H40" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>0.453125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2927,31 +2961,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.934640522875817</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5230769230769231</v>
+        <v>0.4509803921568628</v>
       </c>
       <c r="H41" t="n">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7265625</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2970,31 +3004,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.9490445859872612</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5487179487179488</v>
+        <v>0.4012738853503185</v>
       </c>
       <c r="H42" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0.0703125</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3013,31 +3047,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.8930817610062893</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5076923076923077</v>
+        <v>0.3459119496855346</v>
       </c>
       <c r="H43" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0.803619384765625</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3056,16 +3090,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F44" t="n">
-        <v>0.958974358974359</v>
+        <v>0.949685534591195</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5435897435897435</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="H44" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I44" t="n">
         <v>3</v>
@@ -3080,7 +3114,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3099,31 +3133,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9263803680981595</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5435897435897435</v>
+        <v>0.3558282208588957</v>
       </c>
       <c r="H45" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7265625</v>
+        <v>0.548828125</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3142,31 +3176,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9177215189873418</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5538461538461539</v>
+        <v>0.3481012658227848</v>
       </c>
       <c r="H46" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="I46" t="n">
         <v>5</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>0.7265625</v>
+        <v>0.5810546875</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3185,19 +3219,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9548387096774194</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.3806451612903226</v>
       </c>
       <c r="H47" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>4</v>
@@ -3209,7 +3243,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3228,22 +3262,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="G48" t="n">
-        <v>0.558974358974359</v>
+        <v>0.4213836477987422</v>
       </c>
       <c r="H48" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -3252,7 +3286,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3271,31 +3305,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.3396226415094339</v>
       </c>
       <c r="H49" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>0.453125</v>
+        <v>0.5078125</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3314,31 +3348,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.949685534591195</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4717948717948718</v>
+        <v>0.3144654088050314</v>
       </c>
       <c r="H50" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7265625</v>
+        <v>0.2890625</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3357,31 +3391,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9384615384615385</v>
+        <v>0.9382716049382716</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5538461538461539</v>
+        <v>0.382716049382716</v>
       </c>
       <c r="H51" t="n">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0.021484375</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3400,22 +3434,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="F52" t="n">
-        <v>0.958974358974359</v>
+        <v>0.9207317073170732</v>
       </c>
       <c r="G52" t="n">
-        <v>0.558974358974359</v>
+        <v>0.3353658536585366</v>
       </c>
       <c r="H52" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K52" t="n">
         <v>1</v>
@@ -3424,7 +3458,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3443,22 +3477,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9617834394904459</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.3821656050955414</v>
       </c>
       <c r="H53" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
@@ -3467,7 +3501,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3486,31 +3520,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9329268292682927</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5538461538461539</v>
+        <v>0.4024390243902439</v>
       </c>
       <c r="H54" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="I54" t="n">
+        <v>7</v>
+      </c>
+      <c r="J54" t="n">
         <v>4</v>
       </c>
-      <c r="J54" t="n">
-        <v>5</v>
-      </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0.548828125</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3529,31 +3563,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9536082474226805</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5103092783505154</v>
+        <v>0.4038461538461539</v>
       </c>
       <c r="H55" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="I55" t="n">
         <v>6</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5078125</v>
+        <v>0.2890625</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3572,31 +3606,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9276315789473685</v>
       </c>
       <c r="G56" t="n">
-        <v>0.517948717948718</v>
+        <v>0.4144736842105263</v>
       </c>
       <c r="H56" t="n">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="I56" t="n">
+        <v>7</v>
+      </c>
+      <c r="J56" t="n">
         <v>4</v>
       </c>
-      <c r="J56" t="n">
-        <v>5</v>
-      </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0.548828125</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3615,31 +3649,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9384615384615385</v>
+        <v>0.9483870967741935</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4923076923076923</v>
+        <v>0.3612903225806451</v>
       </c>
       <c r="H57" t="n">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K57" t="n">
-        <v>0.7744140625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3658,31 +3692,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9587628865979382</v>
+        <v>0.9102564102564102</v>
       </c>
       <c r="G58" t="n">
-        <v>0.520618556701031</v>
+        <v>0.3974358974358974</v>
       </c>
       <c r="H58" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K58" t="n">
-        <v>0.7265625</v>
+        <v>0.79052734375</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3701,31 +3735,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9692307692307692</v>
+        <v>0.9025974025974026</v>
       </c>
       <c r="G59" t="n">
-        <v>0.517948717948718</v>
+        <v>0.3896103896103896</v>
       </c>
       <c r="H59" t="n">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0.79052734375</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3744,22 +3778,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9587628865979382</v>
+        <v>0.9240506329113924</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5515463917525774</v>
+        <v>0.3734177215189873</v>
       </c>
       <c r="H60" t="n">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
@@ -3768,7 +3802,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3787,31 +3821,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9426751592356688</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5282051282051282</v>
+        <v>0.4076433121019108</v>
       </c>
       <c r="H61" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2890625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3830,31 +3864,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9435897435897436</v>
+        <v>0.9119496855345912</v>
       </c>
       <c r="G62" t="n">
-        <v>0.5025641025641026</v>
+        <v>0.3459119496855346</v>
       </c>
       <c r="H62" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>0.2265625</v>
+        <v>0.5810546875</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3873,31 +3907,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9587628865979382</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="G63" t="n">
-        <v>0.5309278350515464</v>
+        <v>0.4037267080745341</v>
       </c>
       <c r="H63" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2890625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3916,31 +3950,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.925</v>
       </c>
       <c r="G64" t="n">
-        <v>0.5076923076923077</v>
+        <v>0.3875</v>
       </c>
       <c r="H64" t="n">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>0.453125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3959,31 +3993,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9690721649484536</v>
+        <v>0.94375</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5360824742268041</v>
+        <v>0.39375</v>
       </c>
       <c r="H65" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="I65" t="n">
         <v>4</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>0.6875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4002,31 +4036,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9375</v>
       </c>
       <c r="G66" t="n">
-        <v>0.5538461538461539</v>
+        <v>0.34375</v>
       </c>
       <c r="H66" t="n">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4045,31 +4079,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9627329192546584</v>
       </c>
       <c r="G67" t="n">
-        <v>0.5025641025641026</v>
+        <v>0.3354037267080746</v>
       </c>
       <c r="H67" t="n">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5810546875</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4088,31 +4122,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9432989690721649</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5154639175257731</v>
+        <v>0.3850931677018634</v>
       </c>
       <c r="H68" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K68" t="n">
-        <v>0.75390625</v>
+        <v>0.79052734375</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4131,31 +4165,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9620253164556962</v>
       </c>
       <c r="G69" t="n">
-        <v>0.5487179487179488</v>
+        <v>0.3670886075949367</v>
       </c>
       <c r="H69" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>4</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4174,31 +4208,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9639175257731959</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="G70" t="n">
-        <v>0.5103092783505154</v>
+        <v>0.3459119496855346</v>
       </c>
       <c r="H70" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>0.453125</v>
+        <v>0.0703125</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4217,31 +4251,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9171974522292994</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4769230769230769</v>
+        <v>0.3375796178343949</v>
       </c>
       <c r="H71" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J71" t="n">
         <v>4</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0.266845703125</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4260,31 +4294,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5025641025641026</v>
+        <v>0.3459119496855346</v>
       </c>
       <c r="H72" t="n">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="I72" t="n">
+        <v>6</v>
+      </c>
+      <c r="J72" t="n">
         <v>3</v>
       </c>
-      <c r="J72" t="n">
-        <v>5</v>
-      </c>
       <c r="K72" t="n">
-        <v>0.7265625</v>
+        <v>0.5078125</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4303,31 +4337,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9484536082474226</v>
+        <v>0.9141104294478528</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5</v>
+        <v>0.3374233128834356</v>
       </c>
       <c r="H73" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J73" t="n">
         <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0.4239501953125</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4346,31 +4380,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F74" t="n">
-        <v>0.958974358974359</v>
+        <v>0.9367088607594937</v>
       </c>
       <c r="G74" t="n">
-        <v>0.517948717948718</v>
+        <v>0.3227848101265823</v>
       </c>
       <c r="H74" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J74" t="n">
         <v>3</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4389,22 +4423,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9536082474226805</v>
+        <v>0.9245283018867925</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5154639175257731</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="H75" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
         <v>5</v>
-      </c>
-      <c r="J75" t="n">
-        <v>4</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
@@ -4413,7 +4447,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4432,31 +4466,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9435897435897436</v>
+        <v>0.9367088607594937</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.4113924050632912</v>
       </c>
       <c r="H76" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5078125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4475,31 +4509,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="F77" t="n">
         <v>0.9333333333333333</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4820512820512821</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H77" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J77" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>0.3876953125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4518,31 +4552,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9381443298969072</v>
+        <v>0.9141104294478528</v>
       </c>
       <c r="G78" t="n">
-        <v>0.5309278350515464</v>
+        <v>0.3374233128834356</v>
       </c>
       <c r="H78" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K78" t="n">
-        <v>0.3876953125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4561,31 +4595,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9873417721518988</v>
       </c>
       <c r="G79" t="n">
-        <v>0.5025641025641026</v>
+        <v>0.379746835443038</v>
       </c>
       <c r="H79" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
-        <v>0.7265625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4604,31 +4638,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9150326797385621</v>
+        <v>0.9536082474226805</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3660130718954248</v>
+        <v>0.5773195876288659</v>
       </c>
       <c r="H80" t="n">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="I80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>6</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>0.2890625</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4647,31 +4681,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9484536082474226</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4161490683229814</v>
+        <v>0.5360824742268041</v>
       </c>
       <c r="H81" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="I81" t="n">
         <v>2</v>
       </c>
       <c r="J81" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K81" t="n">
-        <v>0.6875</v>
+        <v>0.1796875</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4690,31 +4724,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9050632911392406</v>
+        <v>0.9378238341968912</v>
       </c>
       <c r="G82" t="n">
-        <v>0.3860759493670886</v>
+        <v>0.5751295336787565</v>
       </c>
       <c r="H82" t="n">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="I82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J82" t="n">
         <v>8</v>
       </c>
       <c r="K82" t="n">
-        <v>0.79052734375</v>
+        <v>0.3876953125</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4733,31 +4767,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9690721649484536</v>
       </c>
       <c r="G83" t="n">
-        <v>0.3397435897435898</v>
+        <v>0.5927835051546392</v>
       </c>
       <c r="H83" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4776,31 +4810,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="F84" t="n">
-        <v>0.930379746835443</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="G84" t="n">
-        <v>0.4050632911392405</v>
+        <v>0.5538461538461539</v>
       </c>
       <c r="H84" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="I84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K84" t="n">
-        <v>0.548828125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4819,22 +4853,22 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="F85" t="n">
-        <v>0.90625</v>
+        <v>0.9639175257731959</v>
       </c>
       <c r="G85" t="n">
-        <v>0.4125</v>
+        <v>0.5927835051546392</v>
       </c>
       <c r="H85" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K85" t="n">
         <v>1</v>
@@ -4843,7 +4877,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4862,22 +4896,22 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9692307692307692</v>
       </c>
       <c r="G86" t="n">
-        <v>0.3806451612903226</v>
+        <v>0.5948717948717949</v>
       </c>
       <c r="H86" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="I86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -4886,7 +4920,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4905,31 +4939,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9135802469135802</v>
+        <v>0.9329896907216495</v>
       </c>
       <c r="G87" t="n">
-        <v>0.3580246913580247</v>
+        <v>0.5876288659793815</v>
       </c>
       <c r="H87" t="n">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="I87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J87" t="n">
         <v>6</v>
       </c>
       <c r="K87" t="n">
-        <v>0.79052734375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4948,31 +4982,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="F88" t="n">
-        <v>0.9430379746835443</v>
+        <v>0.958974358974359</v>
       </c>
       <c r="G88" t="n">
-        <v>0.3481012658227848</v>
+        <v>0.5794871794871795</v>
       </c>
       <c r="H88" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="I88" t="n">
         <v>5</v>
       </c>
       <c r="J88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4991,22 +5025,22 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="F89" t="n">
-        <v>0.925</v>
+        <v>0.9536082474226805</v>
       </c>
       <c r="G89" t="n">
-        <v>0.3875</v>
+        <v>0.5979381443298969</v>
       </c>
       <c r="H89" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="I89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K89" t="n">
         <v>1</v>
@@ -5015,7 +5049,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5034,22 +5068,22 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="F90" t="n">
-        <v>0.9290322580645162</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4129032258064516</v>
+        <v>0.558974358974359</v>
       </c>
       <c r="H90" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="I90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K90" t="n">
         <v>1</v>
@@ -5058,7 +5092,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5077,31 +5111,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9371069182389937</v>
+        <v>0.9435897435897436</v>
       </c>
       <c r="G91" t="n">
-        <v>0.3773584905660378</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="H91" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I91" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K91" t="n">
-        <v>0.34375</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5120,31 +5154,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F92" t="n">
-        <v>0.9433962264150944</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G92" t="n">
-        <v>0.4150943396226415</v>
+        <v>0.5794871794871795</v>
       </c>
       <c r="H92" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I92" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K92" t="n">
-        <v>0.5078125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5163,31 +5197,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9125</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G93" t="n">
-        <v>0.39375</v>
+        <v>0.5435897435897435</v>
       </c>
       <c r="H93" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="I93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K93" t="n">
-        <v>0.5810546875</v>
+        <v>0.5078125</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5206,31 +5240,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4213836477987422</v>
+        <v>0.5794871794871795</v>
       </c>
       <c r="H94" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I94" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K94" t="n">
-        <v>0.3876953125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5249,31 +5283,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.9435897435897436</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3396226415094339</v>
+        <v>0.5487179487179488</v>
       </c>
       <c r="H95" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I95" t="n">
         <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K95" t="n">
-        <v>0.7744140625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5292,31 +5326,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9192546583850931</v>
+        <v>0.958974358974359</v>
       </c>
       <c r="G96" t="n">
-        <v>0.422360248447205</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="H96" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="I96" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K96" t="n">
-        <v>0.7744140625</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5335,31 +5369,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.9435897435897436</v>
       </c>
       <c r="G97" t="n">
-        <v>0.3647798742138365</v>
+        <v>0.5743589743589743</v>
       </c>
       <c r="H97" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I97" t="n">
+        <v>4</v>
+      </c>
+      <c r="J97" t="n">
         <v>6</v>
       </c>
-      <c r="J97" t="n">
-        <v>5</v>
-      </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5378,31 +5412,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="F98" t="n">
-        <v>0.926829268292683</v>
+        <v>0.9794871794871794</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3475609756097561</v>
+        <v>0.5487179487179488</v>
       </c>
       <c r="H98" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
         <v>3</v>
       </c>
-      <c r="J98" t="n">
-        <v>8</v>
-      </c>
       <c r="K98" t="n">
-        <v>0.2265625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5421,16 +5455,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9382716049382716</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G99" t="n">
-        <v>0.3950617283950617</v>
+        <v>0.5487179487179488</v>
       </c>
       <c r="H99" t="n">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="I99" t="n">
         <v>4</v>
@@ -5445,7 +5479,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5464,31 +5498,31 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9503105590062112</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="G100" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.5743589743589743</v>
       </c>
       <c r="H100" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K100" t="n">
-        <v>0.0703125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5507,22 +5541,22 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9447852760736196</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="G101" t="n">
-        <v>0.3803680981595092</v>
+        <v>0.5794871794871795</v>
       </c>
       <c r="H101" t="n">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="I101" t="n">
+        <v>5</v>
+      </c>
+      <c r="J101" t="n">
         <v>4</v>
-      </c>
-      <c r="J101" t="n">
-        <v>5</v>
       </c>
       <c r="K101" t="n">
         <v>1</v>
@@ -5531,7 +5565,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5550,31 +5584,31 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="F102" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.9435897435897436</v>
       </c>
       <c r="G102" t="n">
-        <v>0.3696969696969697</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="H102" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="I102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K102" t="n">
-        <v>0.34375</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5593,31 +5627,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="F103" t="n">
-        <v>0.9503105590062112</v>
+        <v>0.9742268041237113</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3788819875776397</v>
+        <v>0.5515463917525774</v>
       </c>
       <c r="H103" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="I103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>0.453125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5636,31 +5670,31 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="F104" t="n">
-        <v>0.8987341772151899</v>
+        <v>0.9435897435897436</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3291139240506329</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="H104" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="I104" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K104" t="n">
-        <v>0.803619384765625</v>
+        <v>0.2890625</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5679,31 +5713,31 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9435897435897436</v>
       </c>
       <c r="G105" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5692307692307692</v>
       </c>
       <c r="H105" t="n">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>0.1796875</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5722,31 +5756,31 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="F106" t="n">
-        <v>0.9074074074074074</v>
+        <v>0.9329896907216495</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3271604938271605</v>
+        <v>0.5618556701030928</v>
       </c>
       <c r="H106" t="n">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="I106" t="n">
+        <v>4</v>
+      </c>
+      <c r="J106" t="n">
         <v>8</v>
       </c>
-      <c r="J106" t="n">
-        <v>7</v>
-      </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>0.3876953125</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5765,31 +5799,31 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.9641025641025641</v>
       </c>
       <c r="G107" t="n">
-        <v>0.335483870967742</v>
+        <v>0.5846153846153846</v>
       </c>
       <c r="H107" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="I107" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K107" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5808,16 +5842,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="F108" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9639175257731959</v>
       </c>
       <c r="G108" t="n">
-        <v>0.3653846153846154</v>
+        <v>0.5670103092783505</v>
       </c>
       <c r="H108" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="I108" t="n">
         <v>4</v>
@@ -5832,7 +5866,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5851,31 +5885,31 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="F109" t="n">
-        <v>0.9548387096774194</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="G109" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.5692307692307692</v>
       </c>
       <c r="H109" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K109" t="n">
-        <v>1</v>
+        <v>0.5078125</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5894,31 +5928,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="F110" t="n">
-        <v>0.9556962025316456</v>
+        <v>0.9282051282051282</v>
       </c>
       <c r="G110" t="n">
-        <v>0.2911392405063291</v>
+        <v>0.5692307692307692</v>
       </c>
       <c r="H110" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>0.3876953125</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5937,31 +5971,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="F111" t="n">
-        <v>0.9125</v>
+        <v>0.9381443298969072</v>
       </c>
       <c r="G111" t="n">
-        <v>0.38125</v>
+        <v>0.5721649484536082</v>
       </c>
       <c r="H111" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="I111" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>7</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>0.548828125</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5980,31 +6014,31 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="F112" t="n">
-        <v>0.9493670886075949</v>
+        <v>0.958974358974359</v>
       </c>
       <c r="G112" t="n">
-        <v>0.4240506329113924</v>
+        <v>0.5794871794871795</v>
       </c>
       <c r="H112" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>4</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6023,31 +6057,31 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="F113" t="n">
-        <v>0.9559748427672956</v>
+        <v>0.9536082474226805</v>
       </c>
       <c r="G113" t="n">
-        <v>0.4654088050314465</v>
+        <v>0.5979381443298969</v>
       </c>
       <c r="H113" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K113" t="n">
-        <v>0.6875</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6066,31 +6100,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="F114" t="n">
-        <v>0.9375</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="G114" t="n">
-        <v>0.325</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="H114" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K114" t="n">
-        <v>0.75390625</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6109,31 +6143,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="F115" t="n">
-        <v>0.9512195121951219</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="G115" t="n">
-        <v>0.3780487804878049</v>
+        <v>0.5948717948717949</v>
       </c>
       <c r="H115" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2890625</v>
+        <v>0.548828125</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6152,31 +6186,31 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="F116" t="n">
-        <v>0.9207317073170732</v>
+        <v>0.9536082474226805</v>
       </c>
       <c r="G116" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.6185567010309279</v>
       </c>
       <c r="H116" t="n">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="I116" t="n">
+        <v>2</v>
+      </c>
+      <c r="J116" t="n">
         <v>5</v>
       </c>
-      <c r="J116" t="n">
-        <v>8</v>
-      </c>
       <c r="K116" t="n">
-        <v>0.5810546875</v>
+        <v>0.453125</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6195,31 +6229,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="F117" t="n">
-        <v>0.9329268292682927</v>
+        <v>0.9641025641025641</v>
       </c>
       <c r="G117" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.6358974358974359</v>
       </c>
       <c r="H117" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K117" t="n">
-        <v>0.548828125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6238,31 +6272,31 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="F118" t="n">
-        <v>0.9554140127388535</v>
+        <v>0.958974358974359</v>
       </c>
       <c r="G118" t="n">
-        <v>0.3885350318471338</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="H118" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="I118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0.453125</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6281,31 +6315,31 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="F119" t="n">
-        <v>0.934640522875817</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G119" t="n">
-        <v>0.4509803921568628</v>
+        <v>0.5230769230769231</v>
       </c>
       <c r="H119" t="n">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="I119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K119" t="n">
-        <v>0.75390625</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6324,31 +6358,31 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="F120" t="n">
-        <v>0.9490445859872612</v>
+        <v>0.9641025641025641</v>
       </c>
       <c r="G120" t="n">
-        <v>0.4012738853503185</v>
+        <v>0.5487179487179488</v>
       </c>
       <c r="H120" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="I120" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K120" t="n">
-        <v>0.0703125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6367,31 +6401,31 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F121" t="n">
-        <v>0.8930817610062893</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G121" t="n">
-        <v>0.3459119496855346</v>
+        <v>0.5076923076923077</v>
       </c>
       <c r="H121" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I121" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K121" t="n">
-        <v>0.803619384765625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6410,16 +6444,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F122" t="n">
-        <v>0.949685534591195</v>
+        <v>0.958974358974359</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3962264150943396</v>
+        <v>0.5435897435897435</v>
       </c>
       <c r="H122" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I122" t="n">
         <v>3</v>
@@ -6434,7 +6468,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6453,31 +6487,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="F123" t="n">
-        <v>0.9263803680981595</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G123" t="n">
-        <v>0.3558282208588957</v>
+        <v>0.5435897435897435</v>
       </c>
       <c r="H123" t="n">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="I123" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K123" t="n">
-        <v>0.548828125</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6496,31 +6530,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="F124" t="n">
-        <v>0.9177215189873418</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="G124" t="n">
-        <v>0.3481012658227848</v>
+        <v>0.5538461538461539</v>
       </c>
       <c r="H124" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="I124" t="n">
         <v>5</v>
       </c>
       <c r="J124" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K124" t="n">
-        <v>0.5810546875</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6539,19 +6573,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="F125" t="n">
-        <v>0.9548387096774194</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G125" t="n">
-        <v>0.3806451612903226</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="H125" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="I125" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J125" t="n">
         <v>4</v>
@@ -6563,7 +6597,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6582,22 +6616,22 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F126" t="n">
-        <v>0.9433962264150944</v>
+        <v>0.9641025641025641</v>
       </c>
       <c r="G126" t="n">
-        <v>0.4213836477987422</v>
+        <v>0.558974358974359</v>
       </c>
       <c r="H126" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I126" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K126" t="n">
         <v>1</v>
@@ -6606,7 +6640,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6625,31 +6659,31 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F127" t="n">
-        <v>0.9433962264150944</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G127" t="n">
-        <v>0.3396226415094339</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="H127" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I127" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>0.5078125</v>
+        <v>0.453125</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6668,31 +6702,31 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F128" t="n">
-        <v>0.949685534591195</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="G128" t="n">
-        <v>0.3144654088050314</v>
+        <v>0.4717948717948718</v>
       </c>
       <c r="H128" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K128" t="n">
-        <v>0.2890625</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6711,31 +6745,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="F129" t="n">
-        <v>0.9382716049382716</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="G129" t="n">
-        <v>0.382716049382716</v>
+        <v>0.5538461538461539</v>
       </c>
       <c r="H129" t="n">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="I129" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K129" t="n">
-        <v>0.021484375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6754,22 +6788,22 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="F130" t="n">
-        <v>0.9207317073170732</v>
+        <v>0.958974358974359</v>
       </c>
       <c r="G130" t="n">
-        <v>0.3353658536585366</v>
+        <v>0.558974358974359</v>
       </c>
       <c r="H130" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="I130" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J130" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K130" t="n">
         <v>1</v>
@@ -6778,7 +6812,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6797,22 +6831,22 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="F131" t="n">
-        <v>0.9617834394904459</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G131" t="n">
-        <v>0.3821656050955414</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="H131" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="I131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K131" t="n">
         <v>1</v>
@@ -6821,7 +6855,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6840,31 +6874,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="F132" t="n">
-        <v>0.9329268292682927</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4024390243902439</v>
+        <v>0.5538461538461539</v>
       </c>
       <c r="H132" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="I132" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K132" t="n">
-        <v>0.548828125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6883,31 +6917,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="F133" t="n">
-        <v>0.9423076923076923</v>
+        <v>0.9536082474226805</v>
       </c>
       <c r="G133" t="n">
-        <v>0.4038461538461539</v>
+        <v>0.5103092783505154</v>
       </c>
       <c r="H133" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="I133" t="n">
         <v>6</v>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K133" t="n">
-        <v>0.2890625</v>
+        <v>0.5078125</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6926,31 +6960,31 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="F134" t="n">
-        <v>0.9276315789473685</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="G134" t="n">
-        <v>0.4144736842105263</v>
+        <v>0.517948717948718</v>
       </c>
       <c r="H134" t="n">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="I134" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K134" t="n">
-        <v>0.548828125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6969,31 +7003,31 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="F135" t="n">
-        <v>0.9483870967741935</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3612903225806451</v>
+        <v>0.4923076923076923</v>
       </c>
       <c r="H135" t="n">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="I135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J135" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K135" t="n">
-        <v>1</v>
+        <v>0.7744140625</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7012,31 +7046,31 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="F136" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.9587628865979382</v>
       </c>
       <c r="G136" t="n">
-        <v>0.3974358974358974</v>
+        <v>0.520618556701031</v>
       </c>
       <c r="H136" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="I136" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K136" t="n">
-        <v>0.79052734375</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7055,31 +7089,31 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="F137" t="n">
-        <v>0.9025974025974026</v>
+        <v>0.9692307692307692</v>
       </c>
       <c r="G137" t="n">
-        <v>0.3896103896103896</v>
+        <v>0.517948717948718</v>
       </c>
       <c r="H137" t="n">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="I137" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K137" t="n">
-        <v>0.79052734375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7098,22 +7132,22 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="F138" t="n">
-        <v>0.9240506329113924</v>
+        <v>0.9587628865979382</v>
       </c>
       <c r="G138" t="n">
-        <v>0.3734177215189873</v>
+        <v>0.5515463917525774</v>
       </c>
       <c r="H138" t="n">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="I138" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K138" t="n">
         <v>1</v>
@@ -7122,7 +7156,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7141,31 +7175,31 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="F139" t="n">
-        <v>0.9426751592356688</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G139" t="n">
-        <v>0.4076433121019108</v>
+        <v>0.5282051282051282</v>
       </c>
       <c r="H139" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="I139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K139" t="n">
-        <v>1</v>
+        <v>0.2890625</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7184,31 +7218,31 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F140" t="n">
-        <v>0.9119496855345912</v>
+        <v>0.9435897435897436</v>
       </c>
       <c r="G140" t="n">
-        <v>0.3459119496855346</v>
+        <v>0.5025641025641026</v>
       </c>
       <c r="H140" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I140" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J140" t="n">
         <v>8</v>
       </c>
       <c r="K140" t="n">
-        <v>0.5810546875</v>
+        <v>0.2265625</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7227,31 +7261,31 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="F141" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9587628865979382</v>
       </c>
       <c r="G141" t="n">
-        <v>0.4037267080745341</v>
+        <v>0.5309278350515464</v>
       </c>
       <c r="H141" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="I141" t="n">
+        <v>2</v>
+      </c>
+      <c r="J141" t="n">
         <v>6</v>
       </c>
-      <c r="J141" t="n">
-        <v>7</v>
-      </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>0.2890625</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7270,31 +7304,31 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="F142" t="n">
-        <v>0.925</v>
+        <v>0.9641025641025641</v>
       </c>
       <c r="G142" t="n">
-        <v>0.3875</v>
+        <v>0.5076923076923077</v>
       </c>
       <c r="H142" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="I142" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" t="n">
         <v>5</v>
       </c>
-      <c r="J142" t="n">
-        <v>6</v>
-      </c>
       <c r="K142" t="n">
-        <v>1</v>
+        <v>0.453125</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7313,31 +7347,31 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="F143" t="n">
-        <v>0.94375</v>
+        <v>0.9690721649484536</v>
       </c>
       <c r="G143" t="n">
-        <v>0.39375</v>
+        <v>0.5360824742268041</v>
       </c>
       <c r="H143" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="I143" t="n">
         <v>4</v>
       </c>
       <c r="J143" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>1</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7356,31 +7390,31 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="F144" t="n">
-        <v>0.9375</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="G144" t="n">
-        <v>0.34375</v>
+        <v>0.5538461538461539</v>
       </c>
       <c r="H144" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="I144" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7399,31 +7433,31 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="F145" t="n">
-        <v>0.9627329192546584</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G145" t="n">
-        <v>0.3354037267080746</v>
+        <v>0.5025641025641026</v>
       </c>
       <c r="H145" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J145" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K145" t="n">
-        <v>0.6875</v>
+        <v>0.5810546875</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7442,31 +7476,31 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="F146" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9432989690721649</v>
       </c>
       <c r="G146" t="n">
-        <v>0.3850931677018634</v>
+        <v>0.5154639175257731</v>
       </c>
       <c r="H146" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="I146" t="n">
+        <v>4</v>
+      </c>
+      <c r="J146" t="n">
         <v>6</v>
       </c>
-      <c r="J146" t="n">
-        <v>8</v>
-      </c>
       <c r="K146" t="n">
-        <v>0.79052734375</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7485,31 +7519,31 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="F147" t="n">
-        <v>0.9620253164556962</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G147" t="n">
-        <v>0.3670886075949367</v>
+        <v>0.5487179487179488</v>
       </c>
       <c r="H147" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J147" t="n">
         <v>4</v>
       </c>
       <c r="K147" t="n">
-        <v>0.6875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7528,31 +7562,31 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="F148" t="n">
-        <v>0.9433962264150944</v>
+        <v>0.9639175257731959</v>
       </c>
       <c r="G148" t="n">
-        <v>0.3459119496855346</v>
+        <v>0.5103092783505154</v>
       </c>
       <c r="H148" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I148" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>0.0703125</v>
+        <v>0.453125</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7571,31 +7605,31 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="F149" t="n">
-        <v>0.9171974522292994</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="G149" t="n">
-        <v>0.3375796178343949</v>
+        <v>0.4769230769230769</v>
       </c>
       <c r="H149" t="n">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="I149" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J149" t="n">
         <v>4</v>
       </c>
       <c r="K149" t="n">
-        <v>0.266845703125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7614,31 +7648,31 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F150" t="n">
-        <v>0.9433962264150944</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="G150" t="n">
-        <v>0.3459119496855346</v>
+        <v>0.5025641025641026</v>
       </c>
       <c r="H150" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I150" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K150" t="n">
-        <v>0.5078125</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7657,31 +7691,31 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="F151" t="n">
-        <v>0.9141104294478528</v>
+        <v>0.9484536082474226</v>
       </c>
       <c r="G151" t="n">
-        <v>0.3374233128834356</v>
+        <v>0.5</v>
       </c>
       <c r="H151" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="I151" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J151" t="n">
         <v>5</v>
       </c>
       <c r="K151" t="n">
-        <v>0.4239501953125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7700,31 +7734,31 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="F152" t="n">
-        <v>0.9367088607594937</v>
+        <v>0.958974358974359</v>
       </c>
       <c r="G152" t="n">
-        <v>0.3227848101265823</v>
+        <v>0.517948717948718</v>
       </c>
       <c r="H152" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="I152" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
         <v>3</v>
       </c>
       <c r="K152" t="n">
-        <v>0.34375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7743,22 +7777,22 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="F153" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.9536082474226805</v>
       </c>
       <c r="G153" t="n">
-        <v>0.3962264150943396</v>
+        <v>0.5154639175257731</v>
       </c>
       <c r="H153" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="I153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K153" t="n">
         <v>1</v>
@@ -7767,7 +7801,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7786,31 +7820,31 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="F154" t="n">
-        <v>0.9367088607594937</v>
+        <v>0.9435897435897436</v>
       </c>
       <c r="G154" t="n">
-        <v>0.4113924050632912</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="H154" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="I154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J154" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K154" t="n">
-        <v>1</v>
+        <v>0.5078125</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7829,31 +7863,31 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="F155" t="n">
         <v>0.9333333333333333</v>
       </c>
       <c r="G155" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4820512820512821</v>
       </c>
       <c r="H155" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="I155" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J155" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K155" t="n">
-        <v>1</v>
+        <v>0.3876953125</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7872,31 +7906,31 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="F156" t="n">
-        <v>0.9141104294478528</v>
+        <v>0.9381443298969072</v>
       </c>
       <c r="G156" t="n">
-        <v>0.3374233128834356</v>
+        <v>0.5309278350515464</v>
       </c>
       <c r="H156" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="I156" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K156" t="n">
-        <v>1</v>
+        <v>0.3876953125</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7915,25 +7949,25 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="F157" t="n">
-        <v>0.9873417721518988</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G157" t="n">
-        <v>0.379746835443038</v>
+        <v>0.5025641025641026</v>
       </c>
       <c r="H157" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K157" t="n">
-        <v>1</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="158">

--- a/Analysis/Hybrid_Ablation/hybrid_order_reversal.xlsx
+++ b/Analysis/Hybrid_Ablation/hybrid_order_reversal.xlsx
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.003851933044625611</v>
+        <v>-0.003788966910197256</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8383838383838383</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="E2" t="n">
         <v>0.004095884045194398</v>
@@ -669,16 +669,16 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9336717811392492</v>
+        <v>0.9349064745047015</v>
       </c>
       <c r="J2" t="n">
         <v>0.3684153671368089</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.004793475533937497</v>
+        <v>-0.00442701994254191</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="M2" t="n">
         <v>0.008804294662229706</v>
@@ -690,10 +690,10 @@
         <v>252</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0061846018160997</v>
+        <v>-0.006461821371000487</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.875</v>
+        <v>0.9107142857142857</v>
       </c>
       <c r="R2" t="n">
         <v>0.007296962646301697</v>
@@ -705,10 +705,10 @@
         <v>56</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.003851933044625611</v>
+        <v>-0.003788966910197256</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8383838383838383</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="W2" t="n">
         <v>0.004095884045194398</v>
@@ -726,19 +726,19 @@
         <v>5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9253426472485472</v>
+        <v>0.9278428425915694</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9050632911392406</v>
+        <v>0.9113924050632911</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.9304930211750196</v>
+        <v>0.9317544798456859</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.9125</v>
+        <v>0.91875</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.9327113097457209</v>
+        <v>0.9342256811611698</v>
       </c>
       <c r="AG2" t="n">
         <v>0.9025974025974026</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.004512326613520079</v>
+        <v>-0.00416061466115758</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9533799533799534</v>
+        <v>0.9261849261849262</v>
       </c>
       <c r="E4" t="n">
         <v>-0.01578029133102365</v>
@@ -945,16 +945,16 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9613340382412547</v>
+        <v>0.9637324874438277</v>
       </c>
       <c r="J4" t="n">
         <v>0.52128645695656</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001790906687813898</v>
+        <v>0.0015329103885805</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1825396825396825</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="M4" t="n">
         <v>0.03035633095426904</v>
@@ -966,10 +966,10 @@
         <v>252</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004497041420118308</v>
+        <v>0.003681788297172917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="R4" t="n">
         <v>0.03097961867192656</v>
@@ -981,10 +981,10 @@
         <v>56</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.004512326613520079</v>
+        <v>-0.00416061466115758</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9533799533799534</v>
+        <v>0.9261849261849262</v>
       </c>
       <c r="W4" t="n">
         <v>-0.01578029133102365</v>
@@ -1002,10 +1002,10 @@
         <v>5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9563283108643933</v>
+        <v>0.9578720592122654</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9381443298969072</v>
       </c>
       <c r="AD4" t="n">
         <v>0.9835897435897436</v>
@@ -1014,7 +1014,7 @@
         <v>0.9794871794871794</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.9681681205392546</v>
+        <v>0.969197991012424</v>
       </c>
       <c r="AG4" t="n">
         <v>0.9384615384615385</v>
@@ -1032,7 +1032,7 @@
         <v>0.5162865450700501</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.375</v>
+        <v>0.125</v>
       </c>
       <c r="AM4" t="n">
         <v>1</v>
@@ -1044,7 +1044,7 @@
         <v>25</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
@@ -1373,7 +1373,7 @@
         <v>158</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9050632911392406</v>
+        <v>0.9113924050632911</v>
       </c>
       <c r="G4" t="n">
         <v>0.3860759493670886</v>
@@ -1385,10 +1385,10 @@
         <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.79052734375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1502,7 +1502,7 @@
         <v>160</v>
       </c>
       <c r="F7" t="n">
-        <v>0.90625</v>
+        <v>0.9125</v>
       </c>
       <c r="G7" t="n">
         <v>0.4125</v>
@@ -1514,7 +1514,7 @@
         <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -1588,7 +1588,7 @@
         <v>162</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9135802469135802</v>
+        <v>0.9197530864197531</v>
       </c>
       <c r="G9" t="n">
         <v>0.3580246913580247</v>
@@ -1600,10 +1600,10 @@
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.79052734375</v>
+        <v>0.5810546875</v>
       </c>
     </row>
     <row r="10">
@@ -1674,7 +1674,7 @@
         <v>160</v>
       </c>
       <c r="F11" t="n">
-        <v>0.925</v>
+        <v>0.93125</v>
       </c>
       <c r="G11" t="n">
         <v>0.3875</v>
@@ -1683,7 +1683,7 @@
         <v>160</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
         <v>6</v>
@@ -1846,7 +1846,7 @@
         <v>160</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9125</v>
+        <v>0.91875</v>
       </c>
       <c r="G15" t="n">
         <v>0.39375</v>
@@ -1858,10 +1858,10 @@
         <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5810546875</v>
+        <v>0.3876953125</v>
       </c>
     </row>
     <row r="16">
@@ -2018,7 +2018,7 @@
         <v>159</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.9308176100628931</v>
       </c>
       <c r="G19" t="n">
         <v>0.3647798742138365</v>
@@ -2027,7 +2027,7 @@
         <v>159</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
@@ -2061,7 +2061,7 @@
         <v>164</v>
       </c>
       <c r="F20" t="n">
-        <v>0.926829268292683</v>
+        <v>0.9207317073170732</v>
       </c>
       <c r="G20" t="n">
         <v>0.3475609756097561</v>
@@ -2073,10 +2073,10 @@
         <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2265625</v>
+        <v>0.14599609375</v>
       </c>
     </row>
     <row r="21">
@@ -2104,7 +2104,7 @@
         <v>162</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9382716049382716</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="G21" t="n">
         <v>0.3950617283950617</v>
@@ -2113,13 +2113,13 @@
         <v>162</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="22">
@@ -2405,7 +2405,7 @@
         <v>162</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9074074074074074</v>
+        <v>0.9135802469135802</v>
       </c>
       <c r="G28" t="n">
         <v>0.3271604938271605</v>
@@ -2417,10 +2417,10 @@
         <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0.79052734375</v>
       </c>
     </row>
     <row r="29">
@@ -2620,7 +2620,7 @@
         <v>160</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9125</v>
+        <v>0.91875</v>
       </c>
       <c r="G33" t="n">
         <v>0.38125</v>
@@ -2632,7 +2632,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -2835,7 +2835,7 @@
         <v>164</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9207317073170732</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="G38" t="n">
         <v>0.4146341463414634</v>
@@ -2847,10 +2847,10 @@
         <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5810546875</v>
+        <v>0.7744140625</v>
       </c>
     </row>
     <row r="39">
@@ -3050,7 +3050,7 @@
         <v>159</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8930817610062893</v>
+        <v>0.89937106918239</v>
       </c>
       <c r="G43" t="n">
         <v>0.3459119496855346</v>
@@ -3059,13 +3059,13 @@
         <v>159</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
         <v>9</v>
       </c>
       <c r="K43" t="n">
-        <v>0.803619384765625</v>
+        <v>0.6072387695312499</v>
       </c>
     </row>
     <row r="44">
@@ -3093,7 +3093,7 @@
         <v>159</v>
       </c>
       <c r="F44" t="n">
-        <v>0.949685534591195</v>
+        <v>0.9559748427672956</v>
       </c>
       <c r="G44" t="n">
         <v>0.3962264150943396</v>
@@ -3102,13 +3102,13 @@
         <v>159</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="45">
@@ -3136,7 +3136,7 @@
         <v>163</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9263803680981595</v>
+        <v>0.9325153374233128</v>
       </c>
       <c r="G45" t="n">
         <v>0.3558282208588957</v>
@@ -3145,13 +3145,13 @@
         <v>163</v>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
         <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>0.548828125</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="46">
@@ -3695,7 +3695,7 @@
         <v>156</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G58" t="n">
         <v>0.3974358974358974</v>
@@ -3707,10 +3707,10 @@
         <v>8</v>
       </c>
       <c r="J58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>0.79052734375</v>
+        <v>0.5810546875</v>
       </c>
     </row>
     <row r="59">
@@ -3781,7 +3781,7 @@
         <v>158</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9240506329113924</v>
+        <v>0.930379746835443</v>
       </c>
       <c r="G60" t="n">
         <v>0.3734177215189873</v>
@@ -3790,7 +3790,7 @@
         <v>158</v>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
         <v>6</v>
@@ -3824,7 +3824,7 @@
         <v>157</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9426751592356688</v>
+        <v>0.9490445859872612</v>
       </c>
       <c r="G61" t="n">
         <v>0.4076433121019108</v>
@@ -3833,7 +3833,7 @@
         <v>157</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>4</v>
@@ -3867,7 +3867,7 @@
         <v>159</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9119496855345912</v>
+        <v>0.9182389937106918</v>
       </c>
       <c r="G62" t="n">
         <v>0.3459119496855346</v>
@@ -3876,13 +3876,13 @@
         <v>159</v>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
         <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5810546875</v>
+        <v>0.3876953125</v>
       </c>
     </row>
     <row r="63">
@@ -3953,7 +3953,7 @@
         <v>160</v>
       </c>
       <c r="F64" t="n">
-        <v>0.925</v>
+        <v>0.93125</v>
       </c>
       <c r="G64" t="n">
         <v>0.3875</v>
@@ -3962,13 +3962,13 @@
         <v>160</v>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="65">
@@ -4125,7 +4125,7 @@
         <v>161</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9192546583850931</v>
       </c>
       <c r="G68" t="n">
         <v>0.3850931677018634</v>
@@ -4137,10 +4137,10 @@
         <v>6</v>
       </c>
       <c r="J68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K68" t="n">
-        <v>0.79052734375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4340,7 +4340,7 @@
         <v>163</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9141104294478528</v>
+        <v>0.9079754601226994</v>
       </c>
       <c r="G73" t="n">
         <v>0.3374233128834356</v>
@@ -4349,13 +4349,13 @@
         <v>163</v>
       </c>
       <c r="I73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J73" t="n">
         <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>0.4239501953125</v>
+        <v>0.3017578124999999</v>
       </c>
     </row>
     <row r="74">
@@ -4555,7 +4555,7 @@
         <v>163</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9141104294478528</v>
+        <v>0.9202453987730062</v>
       </c>
       <c r="G78" t="n">
         <v>0.3374233128834356</v>
@@ -4567,7 +4567,7 @@
         <v>7</v>
       </c>
       <c r="J78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K78" t="n">
         <v>1</v>
@@ -8004,13 +8004,13 @@
         <v>194</v>
       </c>
       <c r="I158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J158" t="n">
         <v>8</v>
       </c>
       <c r="K158" t="n">
-        <v>0.3876953125</v>
+        <v>0.2265625</v>
       </c>
     </row>
     <row r="159">
@@ -8124,7 +8124,7 @@
         <v>195</v>
       </c>
       <c r="F161" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="G161" t="n">
         <v>0.2102564102564103</v>
@@ -8136,10 +8136,10 @@
         <v>4</v>
       </c>
       <c r="J161" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K161" t="n">
-        <v>0.3876953125</v>
+        <v>0.548828125</v>
       </c>
     </row>
     <row r="162">
@@ -8167,7 +8167,7 @@
         <v>194</v>
       </c>
       <c r="F162" t="n">
-        <v>0.9690721649484536</v>
+        <v>0.9742268041237113</v>
       </c>
       <c r="G162" t="n">
         <v>0.5927835051546392</v>
@@ -8179,7 +8179,7 @@
         <v>3</v>
       </c>
       <c r="J162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K162" t="n">
         <v>1</v>
@@ -8210,7 +8210,7 @@
         <v>194</v>
       </c>
       <c r="F163" t="n">
-        <v>0.9639175257731959</v>
+        <v>0.9690721649484536</v>
       </c>
       <c r="G163" t="n">
         <v>0.5618556701030928</v>
@@ -8222,10 +8222,10 @@
         <v>4</v>
       </c>
       <c r="J163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>1</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="164">
@@ -8262,13 +8262,13 @@
         <v>194</v>
       </c>
       <c r="I164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>1</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="165">
@@ -8339,7 +8339,7 @@
         <v>195</v>
       </c>
       <c r="F166" t="n">
-        <v>0.958974358974359</v>
+        <v>0.9641025641025641</v>
       </c>
       <c r="G166" t="n">
         <v>0.5692307692307692</v>
@@ -8351,7 +8351,7 @@
         <v>4</v>
       </c>
       <c r="J166" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K166" t="n">
         <v>1</v>
@@ -8382,7 +8382,7 @@
         <v>195</v>
       </c>
       <c r="F167" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9692307692307692</v>
       </c>
       <c r="G167" t="n">
         <v>0.558974358974359</v>
@@ -8391,7 +8391,7 @@
         <v>195</v>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J167" t="n">
         <v>3</v>
@@ -8425,7 +8425,7 @@
         <v>195</v>
       </c>
       <c r="F168" t="n">
-        <v>0.9692307692307692</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="G168" t="n">
         <v>0.6358974358974359</v>
@@ -8437,10 +8437,10 @@
         <v>1</v>
       </c>
       <c r="J168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -8468,7 +8468,7 @@
         <v>195</v>
       </c>
       <c r="F169" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="G169" t="n">
         <v>0.6256410256410256</v>
@@ -8480,10 +8480,10 @@
         <v>3</v>
       </c>
       <c r="J169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K169" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="170">
@@ -8511,7 +8511,7 @@
         <v>195</v>
       </c>
       <c r="F170" t="n">
-        <v>0.9692307692307692</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="G170" t="n">
         <v>0.6564102564102564</v>
@@ -8554,7 +8554,7 @@
         <v>195</v>
       </c>
       <c r="F171" t="n">
-        <v>0.9794871794871794</v>
+        <v>0.9846153846153847</v>
       </c>
       <c r="G171" t="n">
         <v>0.6410256410256411</v>
@@ -8566,10 +8566,10 @@
         <v>3</v>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="172">
@@ -8726,7 +8726,7 @@
         <v>195</v>
       </c>
       <c r="F175" t="n">
-        <v>0.9897435897435898</v>
+        <v>0.9846153846153847</v>
       </c>
       <c r="G175" t="n">
         <v>0.6666666666666666</v>
@@ -8738,10 +8738,10 @@
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K175" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="176">
@@ -8769,7 +8769,7 @@
         <v>195</v>
       </c>
       <c r="F176" t="n">
-        <v>0.9897435897435898</v>
+        <v>0.9846153846153847</v>
       </c>
       <c r="G176" t="n">
         <v>0.6871794871794872</v>
@@ -8781,10 +8781,10 @@
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K176" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="177">
@@ -8812,7 +8812,7 @@
         <v>195</v>
       </c>
       <c r="F177" t="n">
-        <v>0.9794871794871794</v>
+        <v>0.9846153846153847</v>
       </c>
       <c r="G177" t="n">
         <v>0.6615384615384615</v>
@@ -8821,13 +8821,13 @@
         <v>195</v>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J177" t="n">
         <v>3</v>
       </c>
       <c r="K177" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="178">
@@ -8996,10 +8996,10 @@
         <v>8</v>
       </c>
       <c r="J181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K181" t="n">
-        <v>0.5810546875</v>
+        <v>0.3876953125</v>
       </c>
     </row>
     <row r="182">
@@ -9070,7 +9070,7 @@
         <v>195</v>
       </c>
       <c r="F183" t="n">
-        <v>0.958974358974359</v>
+        <v>0.9641025641025641</v>
       </c>
       <c r="G183" t="n">
         <v>0.5743589743589743</v>
@@ -9082,7 +9082,7 @@
         <v>3</v>
       </c>
       <c r="J183" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K183" t="n">
         <v>1</v>
@@ -9113,7 +9113,7 @@
         <v>195</v>
       </c>
       <c r="F184" t="n">
-        <v>0.9846153846153847</v>
+        <v>0.9897435897435898</v>
       </c>
       <c r="G184" t="n">
         <v>0.6512820512820513</v>
@@ -9125,7 +9125,7 @@
         <v>1</v>
       </c>
       <c r="J184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K184" t="n">
         <v>1</v>
@@ -9165,10 +9165,10 @@
         <v>195</v>
       </c>
       <c r="I185" t="n">
+        <v>4</v>
+      </c>
+      <c r="J185" t="n">
         <v>3</v>
-      </c>
-      <c r="J185" t="n">
-        <v>4</v>
       </c>
       <c r="K185" t="n">
         <v>1</v>
@@ -9242,7 +9242,7 @@
         <v>194</v>
       </c>
       <c r="F187" t="n">
-        <v>0.9587628865979382</v>
+        <v>0.9639175257731959</v>
       </c>
       <c r="G187" t="n">
         <v>0.5618556701030928</v>
@@ -9251,7 +9251,7 @@
         <v>194</v>
       </c>
       <c r="I187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J187" t="n">
         <v>3</v>
@@ -9371,7 +9371,7 @@
         <v>195</v>
       </c>
       <c r="F190" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.958974358974359</v>
       </c>
       <c r="G190" t="n">
         <v>0.5846153846153846</v>
@@ -9380,13 +9380,13 @@
         <v>195</v>
       </c>
       <c r="I190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J190" t="n">
         <v>3</v>
       </c>
       <c r="K190" t="n">
-        <v>1</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="191">
@@ -9414,7 +9414,7 @@
         <v>195</v>
       </c>
       <c r="F191" t="n">
-        <v>0.9384615384615385</v>
+        <v>0.9435897435897436</v>
       </c>
       <c r="G191" t="n">
         <v>0.2256410256410256</v>
@@ -9457,7 +9457,7 @@
         <v>194</v>
       </c>
       <c r="F192" t="n">
-        <v>0.9742268041237113</v>
+        <v>0.9845360824742269</v>
       </c>
       <c r="G192" t="n">
         <v>0.6030927835051546</v>
@@ -9466,13 +9466,13 @@
         <v>194</v>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J192" t="n">
         <v>3</v>
       </c>
       <c r="K192" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="193">
@@ -9500,7 +9500,7 @@
         <v>195</v>
       </c>
       <c r="F193" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.9692307692307692</v>
       </c>
       <c r="G193" t="n">
         <v>0.6</v>
@@ -9543,7 +9543,7 @@
         <v>195</v>
       </c>
       <c r="F194" t="n">
-        <v>0.9794871794871794</v>
+        <v>0.9846153846153847</v>
       </c>
       <c r="G194" t="n">
         <v>0.6153846153846154</v>
@@ -9595,13 +9595,13 @@
         <v>195</v>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
         <v>3</v>
       </c>
       <c r="K195" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -9629,7 +9629,7 @@
         <v>195</v>
       </c>
       <c r="F196" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.9692307692307692</v>
       </c>
       <c r="G196" t="n">
         <v>0.6358974358974359</v>
@@ -9638,7 +9638,7 @@
         <v>195</v>
       </c>
       <c r="I196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J196" t="n">
         <v>3</v>
@@ -9715,7 +9715,7 @@
         <v>195</v>
       </c>
       <c r="F198" t="n">
-        <v>0.9692307692307692</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="G198" t="n">
         <v>0.6256410256410256</v>
@@ -9767,13 +9767,13 @@
         <v>195</v>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K199" t="n">
-        <v>0.625</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="200">
@@ -9801,7 +9801,7 @@
         <v>195</v>
       </c>
       <c r="F200" t="n">
-        <v>0.9794871794871794</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="G200" t="n">
         <v>0.6461538461538462</v>
@@ -9813,10 +9813,10 @@
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K200" t="n">
-        <v>0.125</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="201">
@@ -9856,10 +9856,10 @@
         <v>1</v>
       </c>
       <c r="J201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K201" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="202">
@@ -9887,7 +9887,7 @@
         <v>195</v>
       </c>
       <c r="F202" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9794871794871794</v>
       </c>
       <c r="G202" t="n">
         <v>0.6615384615384615</v>
@@ -9896,7 +9896,7 @@
         <v>195</v>
       </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>2</v>
@@ -9973,7 +9973,7 @@
         <v>195</v>
       </c>
       <c r="F204" t="n">
-        <v>0.9794871794871794</v>
+        <v>0.9846153846153847</v>
       </c>
       <c r="G204" t="n">
         <v>0.6307692307692307</v>
@@ -10016,7 +10016,7 @@
         <v>195</v>
       </c>
       <c r="F205" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9794871794871794</v>
       </c>
       <c r="G205" t="n">
         <v>0.6461538461538462</v>
@@ -10025,7 +10025,7 @@
         <v>195</v>
       </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>2</v>
@@ -10102,7 +10102,7 @@
         <v>195</v>
       </c>
       <c r="F207" t="n">
-        <v>0.9794871794871794</v>
+        <v>0.9846153846153847</v>
       </c>
       <c r="G207" t="n">
         <v>0.6153846153846154</v>
@@ -10145,7 +10145,7 @@
         <v>195</v>
       </c>
       <c r="F208" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9794871794871794</v>
       </c>
       <c r="G208" t="n">
         <v>0.6307692307692307</v>
@@ -10154,7 +10154,7 @@
         <v>195</v>
       </c>
       <c r="I208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
         <v>2</v>
@@ -10231,7 +10231,7 @@
         <v>195</v>
       </c>
       <c r="F210" t="n">
-        <v>0.9692307692307692</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="G210" t="n">
         <v>0.6</v>
@@ -10317,7 +10317,7 @@
         <v>194</v>
       </c>
       <c r="F212" t="n">
-        <v>0.9639175257731959</v>
+        <v>0.9690721649484536</v>
       </c>
       <c r="G212" t="n">
         <v>0.5721649484536082</v>
@@ -10326,13 +10326,13 @@
         <v>194</v>
       </c>
       <c r="I212" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J212" t="n">
         <v>4</v>
       </c>
       <c r="K212" t="n">
-        <v>1</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="213">
@@ -10446,7 +10446,7 @@
         <v>195</v>
       </c>
       <c r="F215" t="n">
-        <v>0.9846153846153847</v>
+        <v>0.9897435897435898</v>
       </c>
       <c r="G215" t="n">
         <v>0.6153846153846154</v>
@@ -10458,7 +10458,7 @@
         <v>1</v>
       </c>
       <c r="J215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K215" t="n">
         <v>1</v>
@@ -10489,7 +10489,7 @@
         <v>195</v>
       </c>
       <c r="F216" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="G216" t="n">
         <v>0.2102564102564103</v>
@@ -10498,7 +10498,7 @@
         <v>195</v>
       </c>
       <c r="I216" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J216" t="n">
         <v>4</v>
@@ -10541,13 +10541,13 @@
         <v>194</v>
       </c>
       <c r="I217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K217" t="n">
-        <v>0.453125</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="218">
@@ -10575,7 +10575,7 @@
         <v>195</v>
       </c>
       <c r="F218" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.9692307692307692</v>
       </c>
       <c r="G218" t="n">
         <v>0.5846153846153846</v>
@@ -10584,13 +10584,13 @@
         <v>195</v>
       </c>
       <c r="I218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
         <v>5</v>
       </c>
       <c r="K218" t="n">
-        <v>0.453125</v>
+        <v>0.21875</v>
       </c>
     </row>
     <row r="219">
@@ -10618,7 +10618,7 @@
         <v>195</v>
       </c>
       <c r="F219" t="n">
-        <v>0.9897435897435898</v>
+        <v>0.9846153846153847</v>
       </c>
       <c r="G219" t="n">
         <v>0.5897435897435898</v>
@@ -10630,10 +10630,10 @@
         <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K219" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="220">
@@ -10747,7 +10747,7 @@
         <v>194</v>
       </c>
       <c r="F222" t="n">
-        <v>0.9639175257731959</v>
+        <v>0.9690721649484536</v>
       </c>
       <c r="G222" t="n">
         <v>0.6082474226804123</v>
@@ -10756,13 +10756,13 @@
         <v>194</v>
       </c>
       <c r="I222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J222" t="n">
         <v>4</v>
       </c>
       <c r="K222" t="n">
-        <v>1</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="223">
@@ -10876,7 +10876,7 @@
         <v>195</v>
       </c>
       <c r="F225" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9692307692307692</v>
       </c>
       <c r="G225" t="n">
         <v>0.5897435897435898</v>
@@ -10885,7 +10885,7 @@
         <v>195</v>
       </c>
       <c r="I225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J225" t="n">
         <v>3</v>
@@ -10962,7 +10962,7 @@
         <v>194</v>
       </c>
       <c r="F227" t="n">
-        <v>0.9742268041237113</v>
+        <v>0.979381443298969</v>
       </c>
       <c r="G227" t="n">
         <v>0.6082474226804123</v>
@@ -10971,13 +10971,13 @@
         <v>194</v>
       </c>
       <c r="I227" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J227" t="n">
         <v>3</v>
       </c>
       <c r="K227" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="228">
@@ -11091,7 +11091,7 @@
         <v>195</v>
       </c>
       <c r="F230" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9692307692307692</v>
       </c>
       <c r="G230" t="n">
         <v>0.6153846153846154</v>
@@ -11100,7 +11100,7 @@
         <v>195</v>
       </c>
       <c r="I230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J230" t="n">
         <v>3</v>
@@ -11177,7 +11177,7 @@
         <v>194</v>
       </c>
       <c r="F232" t="n">
-        <v>0.9536082474226805</v>
+        <v>0.9587628865979382</v>
       </c>
       <c r="G232" t="n">
         <v>0.5309278350515464</v>
@@ -11186,13 +11186,13 @@
         <v>194</v>
       </c>
       <c r="I232" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J232" t="n">
         <v>5</v>
       </c>
       <c r="K232" t="n">
-        <v>1</v>
+        <v>0.7265625</v>
       </c>
     </row>
     <row r="233">
@@ -11306,7 +11306,7 @@
         <v>195</v>
       </c>
       <c r="F235" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9794871794871794</v>
       </c>
       <c r="G235" t="n">
         <v>0.5692307692307692</v>
@@ -11318,7 +11318,7 @@
         <v>2</v>
       </c>
       <c r="J235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K235" t="n">
         <v>1</v>
